--- a/Carbon_Pathways_Inputs_Sample.xlsx
+++ b/Carbon_Pathways_Inputs_Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theca\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDB81DA-AAAA-4356-8DEC-F2E277326F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05EDEE1-77C8-4FE6-8CD9-7CC7529A8FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input_Params" sheetId="1" r:id="rId1"/>
@@ -2078,24 +2078,19 @@
         <v>1495</v>
       </c>
       <c r="E6" s="2">
-        <f>D6-(D6*0.0375)</f>
-        <v>1438.9375</v>
+        <v>1392.09</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" ref="F6:I6" si="3">E6-(E6*0.0375)</f>
-        <v>1384.97734375</v>
+        <v>1296.27</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="3"/>
-        <v>1333.0406933593752</v>
+        <v>1207.04</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="3"/>
-        <v>1283.0516673583986</v>
+        <v>1123.96</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" si="3"/>
-        <v>1234.9372298324586</v>
+        <v>1046.5899999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -2141,24 +2136,19 @@
         <v>1360</v>
       </c>
       <c r="E8" s="2">
-        <f>D8-(D8*0.095)</f>
-        <v>1230.8</v>
+        <v>1203.5999999999999</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" ref="F8:I8" si="4">E8-(E8*0.095)</f>
-        <v>1113.874</v>
+        <v>1065.19</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" si="4"/>
-        <v>1008.05597</v>
+        <v>942.69</v>
       </c>
       <c r="H8" s="2">
-        <f t="shared" si="4"/>
-        <v>912.29065285000001</v>
+        <v>834.28</v>
       </c>
       <c r="I8" s="2">
-        <f t="shared" si="4"/>
-        <v>825.62304082925004</v>
+        <v>738.34</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -2237,19 +2227,19 @@
         <v>5880</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" ref="F11:I11" si="5">E11-(E11*0.02)</f>
+        <f t="shared" ref="F11:I11" si="3">E11-(E11*0.02)</f>
         <v>5762.4</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>5647.152</v>
       </c>
       <c r="H11" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>5534.2089599999999</v>
       </c>
       <c r="I11" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>5423.5247808000004</v>
       </c>
     </row>
